--- a/edp/edp_schema_main_v0.1.xlsx
+++ b/edp/edp_schema_main_v0.1.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zef22hak/development/COPO_refactoring/COPO-production/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EF076F-1C0C-934F-B365-D9D2B6520CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4F4FB0-5764-BA48-9ACD-CEA59B0FD471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38940" yWindow="1940" windowWidth="30240" windowHeight="18880" activeTab="3" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="allowed_values" sheetId="2" r:id="rId2"/>
     <sheet name="checklists" sheetId="6" r:id="rId3"/>
     <sheet name="components" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId5"/>
+    <sheet name="checklists_filter" sheetId="10" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$W$51</definedName>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="263">
   <si>
     <t>component_name</t>
   </si>
@@ -731,12 +731,6 @@
     <t>If custom indices were used, please enter their sequence.</t>
   </si>
   <si>
-    <t>Has the library been AMPure cleaned at least twice?</t>
-  </si>
-  <si>
-    <t>Please select Yes or No from drop down menu.</t>
-  </si>
-  <si>
     <t>If used, enter the name of the first PacBio adapter index, e.g.,bc2001.
 If custom indices were used, please also supply the index sequence in column F of the Index Information sheet.</t>
   </si>
@@ -910,9 +904,6 @@
     <t>QC Datum:A260230</t>
   </si>
   <si>
-    <t>Experiment -&gt; assign plate</t>
-  </si>
-  <si>
     <t>By submitting this manifest to EI you are confirming that, if relevant, you have informed us of any potential health and safety risks associated with the samples. Please select YES (in the box to the right) to confirm you have read and understood this message.</t>
   </si>
   <si>
@@ -1010,6 +1001,60 @@
   </si>
   <si>
     <t>first_data_line_no</t>
+  </si>
+  <si>
+    <t>sample_type</t>
+  </si>
+  <si>
+    <t>gDNA</t>
+  </si>
+  <si>
+    <t>Amplicon</t>
+  </si>
+  <si>
+    <t>Tailed amplicon</t>
+  </si>
+  <si>
+    <t>cDNA</t>
+  </si>
+  <si>
+    <t>Total RNA</t>
+  </si>
+  <si>
+    <t>rRNA depleted RNA</t>
+  </si>
+  <si>
+    <t>mRNA enriched RNA</t>
+  </si>
+  <si>
+    <t>miRNA enriched RNA</t>
+  </si>
+  <si>
+    <t>Pre-made library</t>
+  </si>
+  <si>
+    <t>Illumina premade library</t>
+  </si>
+  <si>
+    <t>Pool</t>
+  </si>
+  <si>
+    <t>PacBio  premade library</t>
+  </si>
+  <si>
+    <t>Cell Lysate</t>
+  </si>
+  <si>
+    <t>Agarose plug</t>
+  </si>
+  <si>
+    <t>Bacterial Culture</t>
+  </si>
+  <si>
+    <t>Tissue</t>
+  </si>
+  <si>
+    <t>Pre-made library pool</t>
   </si>
 </sst>
 </file>
@@ -1136,16 +1181,15 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FFA31515"/>
       <name val="Menlo"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1401,10 +1445,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1428,6 +1468,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1820,7 +1861,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>4</v>
@@ -1853,28 +1894,28 @@
         <v>119</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="R1" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="S1" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="T1" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="U1" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="V1" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="W1" s="43" t="s">
-        <v>181</v>
+      <c r="V1" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="W1" s="42" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="16">
@@ -1903,25 +1944,25 @@
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q2" s="2"/>
-      <c r="R2" s="44" t="s">
+      <c r="R2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="S2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="44" t="s">
+      <c r="T2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="44" t="s">
+      <c r="U2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="44" t="s">
+      <c r="V2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W2" s="44" t="s">
+      <c r="W2" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1933,13 +1974,13 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F3" s="1" t="b">
         <v>0</v>
@@ -1952,7 +1993,7 @@
         <v>138</v>
       </c>
       <c r="L3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
@@ -1961,22 +2002,22 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="44" t="s">
+      <c r="R3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="44" t="s">
+      <c r="S3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="44" t="s">
+      <c r="T3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="44" t="s">
+      <c r="U3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="44" t="s">
+      <c r="V3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="44" t="s">
+      <c r="W3" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1994,7 +2035,7 @@
         <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F4" s="1" t="b">
         <v>0</v>
@@ -2012,22 +2053,22 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="44" t="s">
+      <c r="R4" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S4" s="44" t="s">
+      <c r="S4" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="44" t="s">
+      <c r="T4" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="44" t="s">
+      <c r="U4" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="44" t="s">
+      <c r="V4" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="44" t="s">
+      <c r="W4" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2039,13 +2080,13 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F5" s="1" t="b">
         <v>0</v>
@@ -2060,15 +2101,15 @@
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q5" s="2"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
     </row>
     <row r="6" spans="1:23" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
@@ -2084,33 +2125,33 @@
         <v>96</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N6" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="44" t="s">
+      <c r="R6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S6" s="44" t="s">
+      <c r="S6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T6" s="44" t="s">
+      <c r="T6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U6" s="44" t="s">
+      <c r="U6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V6" s="44" t="s">
+      <c r="V6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W6" s="44" t="s">
+      <c r="W6" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2128,7 +2169,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F7" s="1" t="b">
         <v>1</v>
@@ -2138,24 +2179,24 @@
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="R7" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="R7" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S7" s="44" t="s">
+      <c r="S7" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="44" t="s">
+      <c r="T7" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U7" s="44" t="s">
+      <c r="U7" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V7" s="44" t="s">
+      <c r="V7" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W7" s="44" t="s">
+      <c r="W7" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2173,7 +2214,7 @@
         <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F8" s="1" t="b">
         <v>0</v>
@@ -2189,25 +2230,25 @@
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q8" s="3"/>
-      <c r="R8" s="44" t="s">
+      <c r="R8" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S8" s="44" t="s">
+      <c r="S8" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T8" s="44" t="s">
+      <c r="T8" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="44" t="s">
+      <c r="U8" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V8" s="44" t="s">
+      <c r="V8" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W8" s="44" t="s">
+      <c r="W8" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2219,13 +2260,13 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F9" s="1" t="b">
         <v>0</v>
@@ -2240,25 +2281,25 @@
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q9" s="3"/>
-      <c r="R9" s="44" t="s">
+      <c r="R9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="44" t="s">
+      <c r="S9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T9" s="44" t="s">
+      <c r="T9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U9" s="44" t="s">
+      <c r="U9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V9" s="44" t="s">
+      <c r="V9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W9" s="44" t="s">
+      <c r="W9" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2276,7 +2317,7 @@
         <v>43</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F10" s="1" t="b">
         <v>0</v>
@@ -2291,25 +2332,25 @@
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q10" s="3"/>
-      <c r="R10" s="44" t="s">
+      <c r="R10" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="S10" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="T10" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="U10" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="V10" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="W10" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2327,7 +2368,7 @@
         <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F11" s="1" t="b">
         <v>0</v>
@@ -2342,25 +2383,25 @@
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q11" s="3"/>
-      <c r="R11" s="44" t="s">
+      <c r="R11" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S11" s="44" t="s">
+      <c r="S11" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T11" s="44" t="s">
+      <c r="T11" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U11" s="44" t="s">
+      <c r="U11" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V11" s="44" t="s">
+      <c r="V11" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W11" s="44" t="s">
+      <c r="W11" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2378,7 +2419,7 @@
         <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F12" s="1" t="b">
         <v>0</v>
@@ -2393,25 +2434,25 @@
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q12" s="3"/>
-      <c r="R12" s="44" t="s">
+      <c r="R12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S12" s="44" t="s">
+      <c r="S12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T12" s="44" t="s">
+      <c r="T12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U12" s="44" t="s">
+      <c r="U12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V12" s="44" t="s">
+      <c r="V12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W12" s="44" t="s">
+      <c r="W12" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2429,7 +2470,7 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F13" s="1" t="b">
         <v>0</v>
@@ -2444,21 +2485,21 @@
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q13" s="2"/>
-      <c r="R13" s="44" t="s">
+      <c r="R13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S13" s="44" t="s">
+      <c r="S13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T13" s="44" t="s">
+      <c r="T13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U13" s="44"/>
-      <c r="V13" s="44"/>
-      <c r="W13" s="44"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
     </row>
     <row r="14" spans="1:23" ht="15.75" customHeight="1">
       <c r="A14" s="19" t="s">
@@ -2491,25 +2532,25 @@
       </c>
       <c r="O14" s="19"/>
       <c r="P14" s="19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q14" s="19"/>
-      <c r="R14" s="44" t="s">
+      <c r="R14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S14" s="44" t="s">
+      <c r="S14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T14" s="44" t="s">
+      <c r="T14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U14" s="44" t="s">
+      <c r="U14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V14" s="44" t="s">
+      <c r="V14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W14" s="44" t="s">
+      <c r="W14" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2527,7 +2568,7 @@
         <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F15" s="1" t="b">
         <v>0</v>
@@ -2549,22 +2590,22 @@
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="44" t="s">
+      <c r="R15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S15" s="44" t="s">
+      <c r="S15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T15" s="44" t="s">
+      <c r="T15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U15" s="44" t="s">
+      <c r="U15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V15" s="44" t="s">
+      <c r="V15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W15" s="44" t="s">
+      <c r="W15" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2582,7 +2623,7 @@
         <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F16" s="1" t="b">
         <v>0</v>
@@ -2595,7 +2636,7 @@
         <v>117</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
@@ -2604,22 +2645,22 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="44" t="s">
+      <c r="R16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S16" s="44" t="s">
+      <c r="S16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T16" s="44" t="s">
+      <c r="T16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U16" s="44" t="s">
+      <c r="U16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V16" s="44" t="s">
+      <c r="V16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W16" s="44" t="s">
+      <c r="W16" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2636,8 +2677,8 @@
       <c r="D17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="47" t="s">
-        <v>243</v>
+      <c r="E17" s="46" t="s">
+        <v>240</v>
       </c>
       <c r="F17" s="1" t="b">
         <v>0</v>
@@ -2650,7 +2691,7 @@
         <v>117</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
@@ -2659,22 +2700,22 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="44" t="s">
+      <c r="R17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S17" s="44" t="s">
+      <c r="S17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T17" s="44" t="s">
+      <c r="T17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U17" s="44" t="s">
+      <c r="U17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V17" s="44" t="s">
+      <c r="V17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W17" s="44"/>
+      <c r="W17" s="43"/>
     </row>
     <row r="18" spans="1:23" ht="17">
       <c r="A18" t="s">
@@ -2687,10 +2728,10 @@
         <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F18" s="1" t="b">
         <v>0</v>
@@ -2708,22 +2749,22 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="44" t="s">
+      <c r="R18" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S18" s="44" t="s">
+      <c r="S18" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T18" s="44" t="s">
+      <c r="T18" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U18" s="44" t="s">
+      <c r="U18" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="44" t="s">
+      <c r="V18" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W18" s="44"/>
+      <c r="W18" s="43"/>
     </row>
     <row r="19" spans="1:23" ht="17">
       <c r="A19" t="s">
@@ -2739,7 +2780,7 @@
         <v>141</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F19" s="1" t="b">
         <v>0</v>
@@ -2757,16 +2798,16 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44" t="s">
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V19" s="44" t="s">
+      <c r="V19" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W19" s="44"/>
+      <c r="W19" s="43"/>
     </row>
     <row r="20" spans="1:23" ht="17">
       <c r="A20" t="s">
@@ -2782,7 +2823,7 @@
         <v>143</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F20" s="1" t="b">
         <v>0</v>
@@ -2800,16 +2841,16 @@
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="44"/>
-      <c r="T20" s="44"/>
-      <c r="U20" s="44" t="s">
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V20" s="44" t="s">
+      <c r="V20" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W20" s="44"/>
+      <c r="W20" s="43"/>
     </row>
     <row r="21" spans="1:23" ht="14" customHeight="1">
       <c r="A21" t="s">
@@ -2825,7 +2866,7 @@
         <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F21" s="1" t="b">
         <v>0</v>
@@ -2843,22 +2884,22 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="10"/>
-      <c r="R21" s="44" t="s">
+      <c r="R21" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S21" s="44" t="s">
+      <c r="S21" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T21" s="44" t="s">
+      <c r="T21" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U21" s="44" t="s">
+      <c r="U21" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V21" s="44" t="s">
+      <c r="V21" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W21" s="44" t="s">
+      <c r="W21" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2876,7 +2917,7 @@
         <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F22" s="1" t="b">
         <v>0</v>
@@ -2894,22 +2935,22 @@
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="3"/>
-      <c r="R22" s="44" t="s">
+      <c r="R22" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S22" s="44" t="s">
+      <c r="S22" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T22" s="44" t="s">
+      <c r="T22" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U22" s="44" t="s">
+      <c r="U22" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V22" s="44" t="s">
+      <c r="V22" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W22" s="44" t="s">
+      <c r="W22" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2936,25 +2977,25 @@
       <c r="N23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="O23" s="48"/>
+      <c r="O23" s="47"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="44" t="s">
+      <c r="R23" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S23" s="44" t="s">
+      <c r="S23" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T23" s="44" t="s">
+      <c r="T23" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U23" s="44" t="s">
+      <c r="U23" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V23" s="44" t="s">
+      <c r="V23" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W23" s="44" t="s">
+      <c r="W23" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2972,7 +3013,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F24" s="1" t="b">
         <v>0</v>
@@ -2990,22 +3031,22 @@
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="3"/>
-      <c r="R24" s="44" t="s">
+      <c r="R24" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S24" s="44" t="s">
+      <c r="S24" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T24" s="44" t="s">
+      <c r="T24" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U24" s="44" t="s">
+      <c r="U24" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V24" s="44" t="s">
+      <c r="V24" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W24" s="44" t="s">
+      <c r="W24" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3023,13 +3064,13 @@
         <v>149</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F25" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -3041,16 +3082,16 @@
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="3"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
-      <c r="T25" s="44"/>
-      <c r="U25" s="44" t="s">
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V25" s="44" t="s">
+      <c r="V25" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W25" s="44" t="s">
+      <c r="W25" s="43" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3068,13 +3109,13 @@
         <v>151</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -3086,16 +3127,16 @@
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="3"/>
-      <c r="R26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44" t="s">
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V26" s="44" t="s">
+      <c r="V26" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="W26" s="44" t="s">
+      <c r="W26" s="43" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3107,19 +3148,19 @@
         <v>14</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -3131,14 +3172,14 @@
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="3"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="44"/>
-      <c r="T27" s="44"/>
-      <c r="U27" s="44"/>
-      <c r="V27" s="44" t="s">
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="43"/>
+      <c r="V27" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W27" s="44"/>
+      <c r="W27" s="43"/>
     </row>
     <row r="28" spans="1:23" ht="17">
       <c r="A28" t="s">
@@ -3154,13 +3195,13 @@
         <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -3172,12 +3213,12 @@
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="44" t="s">
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="43"/>
+      <c r="W28" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3189,19 +3230,19 @@
         <v>14</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F29" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -3213,12 +3254,12 @@
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="3"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="44"/>
-      <c r="U29" s="44"/>
-      <c r="V29" s="44"/>
-      <c r="W29" s="44" t="s">
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="43"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="43"/>
+      <c r="W29" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3236,7 +3277,7 @@
         <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F30" s="1" t="b">
         <v>0</v>
@@ -3256,22 +3297,22 @@
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="3"/>
-      <c r="R30" s="44" t="s">
+      <c r="R30" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S30" s="44" t="s">
+      <c r="S30" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T30" s="44" t="s">
+      <c r="T30" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U30" s="44" t="s">
+      <c r="U30" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V30" s="44" t="s">
+      <c r="V30" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="W30" s="44" t="s">
+      <c r="W30" s="43" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3289,7 +3330,7 @@
         <v>66</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F31" s="1" t="b">
         <v>0</v>
@@ -3307,20 +3348,20 @@
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="3"/>
-      <c r="R31" s="44" t="s">
+      <c r="R31" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S31" s="44" t="s">
+      <c r="S31" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T31" s="44" t="s">
+      <c r="T31" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U31" s="44"/>
-      <c r="V31" s="44" t="s">
+      <c r="U31" s="43"/>
+      <c r="V31" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="W31" s="44" t="s">
+      <c r="W31" s="43" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3338,7 +3379,7 @@
         <v>68</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F32" s="1" t="b">
         <v>0</v>
@@ -3356,22 +3397,22 @@
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="44" t="s">
+      <c r="R32" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S32" s="44" t="s">
+      <c r="S32" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T32" s="44" t="s">
+      <c r="T32" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U32" s="44" t="s">
+      <c r="U32" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="V32" s="44" t="s">
+      <c r="V32" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W32" s="44" t="s">
+      <c r="W32" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3389,7 +3430,7 @@
         <v>70</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F33" s="1" t="b">
         <v>0</v>
@@ -3409,22 +3450,22 @@
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="3"/>
-      <c r="R33" s="44" t="s">
+      <c r="R33" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S33" s="44" t="s">
+      <c r="S33" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T33" s="44" t="s">
+      <c r="T33" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U33" s="44" t="s">
+      <c r="U33" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V33" s="44" t="s">
+      <c r="V33" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W33" s="44" t="s">
+      <c r="W33" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3442,13 +3483,13 @@
         <v>153</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="15"/>
@@ -3460,16 +3501,16 @@
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="3"/>
-      <c r="R34" s="44"/>
-      <c r="S34" s="44"/>
-      <c r="T34" s="44"/>
-      <c r="U34" s="44" t="s">
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V34" s="44" t="s">
+      <c r="V34" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W34" s="44" t="s">
+      <c r="W34" s="43" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3487,7 +3528,7 @@
         <v>72</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F35" s="1" t="b">
         <v>0</v>
@@ -3507,22 +3548,22 @@
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="3"/>
-      <c r="R35" s="44" t="s">
+      <c r="R35" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S35" s="44" t="s">
+      <c r="S35" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T35" s="44" t="s">
+      <c r="T35" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U35" s="44" t="s">
+      <c r="U35" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V35" s="44" t="s">
+      <c r="V35" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W35" s="44" t="s">
+      <c r="W35" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3540,7 +3581,7 @@
         <v>74</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F36" s="1" t="b">
         <v>0</v>
@@ -3558,22 +3599,22 @@
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="3"/>
-      <c r="R36" s="44" t="s">
+      <c r="R36" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S36" s="44" t="s">
+      <c r="S36" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T36" s="44" t="s">
+      <c r="T36" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U36" s="44" t="s">
+      <c r="U36" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V36" s="44" t="s">
+      <c r="V36" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W36" s="44" t="s">
+      <c r="W36" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3591,7 +3632,7 @@
         <v>136</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F37" s="1" t="b">
         <v>0</v>
@@ -3609,22 +3650,22 @@
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="3"/>
-      <c r="R37" s="44" t="s">
+      <c r="R37" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S37" s="44" t="s">
+      <c r="S37" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T37" s="44" t="s">
+      <c r="T37" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U37" s="44" t="s">
+      <c r="U37" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V37" s="44" t="s">
+      <c r="V37" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W37" s="44" t="s">
+      <c r="W37" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3642,7 +3683,7 @@
         <v>76</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F38" s="1" t="b">
         <v>0</v>
@@ -3660,22 +3701,22 @@
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="3"/>
-      <c r="R38" s="44" t="s">
+      <c r="R38" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S38" s="44" t="s">
+      <c r="S38" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T38" s="44" t="s">
+      <c r="T38" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U38" s="44" t="s">
+      <c r="U38" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="V38" s="44" t="s">
+      <c r="V38" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W38" s="44" t="s">
+      <c r="W38" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3710,21 +3751,21 @@
       </c>
       <c r="O39" s="19"/>
       <c r="P39" s="19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q39" s="19"/>
-      <c r="R39" s="44" t="s">
+      <c r="R39" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S39" s="44" t="s">
+      <c r="S39" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T39" s="44" t="s">
+      <c r="T39" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U39" s="44"/>
-      <c r="V39" s="44"/>
-      <c r="W39" s="44"/>
+      <c r="U39" s="43"/>
+      <c r="V39" s="43"/>
+      <c r="W39" s="43"/>
     </row>
     <row r="40" spans="1:23" ht="18" customHeight="1">
       <c r="A40" s="34" t="s">
@@ -3740,7 +3781,7 @@
         <v>25</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F40" s="1" t="b">
         <v>0</v>
@@ -3761,18 +3802,18 @@
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="44" t="s">
+      <c r="R40" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S40" s="44" t="s">
+      <c r="S40" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T40" s="44" t="s">
+      <c r="T40" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U40" s="45"/>
-      <c r="V40" s="45"/>
-      <c r="W40" s="45"/>
+      <c r="U40" s="44"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="44"/>
     </row>
     <row r="41" spans="1:23" ht="14" customHeight="1">
       <c r="A41" s="34" t="s">
@@ -3788,7 +3829,7 @@
         <v>79</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F41" s="1" t="b">
         <v>0</v>
@@ -3810,20 +3851,20 @@
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="44" t="s">
+      <c r="R41" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S41" s="44" t="s">
+      <c r="S41" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T41" s="44" t="s">
+      <c r="T41" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U41" s="45"/>
-      <c r="V41" s="45"/>
-      <c r="W41" s="45"/>
-    </row>
-    <row r="42" spans="1:23" s="39" customFormat="1" ht="34">
+      <c r="U41" s="44"/>
+      <c r="V41" s="44"/>
+      <c r="W41" s="44"/>
+    </row>
+    <row r="42" spans="1:23" s="38" customFormat="1" ht="34">
       <c r="A42" s="34" t="s">
         <v>40</v>
       </c>
@@ -3840,10 +3881,10 @@
       <c r="F42" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
       <c r="I42" s="32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J42" s="35"/>
       <c r="K42" s="35"/>
@@ -3854,17 +3895,17 @@
       </c>
       <c r="O42" s="35"/>
       <c r="P42" s="35"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="44" t="s">
+      <c r="Q42" s="40"/>
+      <c r="R42" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S42" s="44"/>
-      <c r="T42" s="44"/>
-      <c r="U42" s="45"/>
-      <c r="V42" s="45"/>
-      <c r="W42" s="45"/>
-    </row>
-    <row r="43" spans="1:23" s="39" customFormat="1" ht="51">
+      <c r="S42" s="43"/>
+      <c r="T42" s="43"/>
+      <c r="U42" s="44"/>
+      <c r="V42" s="44"/>
+      <c r="W42" s="44"/>
+    </row>
+    <row r="43" spans="1:23" s="38" customFormat="1" ht="51">
       <c r="A43" s="34" t="s">
         <v>40</v>
       </c>
@@ -3881,10 +3922,10 @@
       <c r="F43" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
       <c r="I43" s="32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J43" s="35"/>
       <c r="K43" s="35"/>
@@ -3895,15 +3936,15 @@
       </c>
       <c r="O43" s="35"/>
       <c r="P43" s="35"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="44" t="s">
+      <c r="Q43" s="40"/>
+      <c r="R43" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="S43" s="44"/>
-      <c r="T43" s="44"/>
-      <c r="U43" s="45"/>
-      <c r="V43" s="45"/>
-      <c r="W43" s="45"/>
+      <c r="S43" s="43"/>
+      <c r="T43" s="43"/>
+      <c r="U43" s="44"/>
+      <c r="V43" s="44"/>
+      <c r="W43" s="44"/>
     </row>
     <row r="44" spans="1:23" ht="17">
       <c r="A44" s="5" t="s">
@@ -3934,16 +3975,16 @@
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="3"/>
-      <c r="R44" s="44"/>
-      <c r="S44" s="44" t="s">
+      <c r="R44" s="43"/>
+      <c r="S44" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T44" s="44" t="s">
+      <c r="T44" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U44" s="45"/>
-      <c r="V44" s="45"/>
-      <c r="W44" s="45"/>
+      <c r="U44" s="44"/>
+      <c r="V44" s="44"/>
+      <c r="W44" s="44"/>
     </row>
     <row r="45" spans="1:23" ht="142" customHeight="1">
       <c r="A45" s="5" t="s">
@@ -3974,16 +4015,16 @@
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" s="3"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="44" t="s">
+      <c r="R45" s="43"/>
+      <c r="S45" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T45" s="44" t="s">
+      <c r="T45" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U45" s="45"/>
-      <c r="V45" s="45"/>
-      <c r="W45" s="45"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="44"/>
     </row>
     <row r="46" spans="1:23" ht="17">
       <c r="A46" s="5" t="s">
@@ -4014,16 +4055,16 @@
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="3"/>
-      <c r="R46" s="44"/>
-      <c r="S46" s="44" t="s">
+      <c r="R46" s="43"/>
+      <c r="S46" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T46" s="44" t="s">
+      <c r="T46" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U46" s="45"/>
-      <c r="V46" s="45"/>
-      <c r="W46" s="45"/>
+      <c r="U46" s="44"/>
+      <c r="V46" s="44"/>
+      <c r="W46" s="44"/>
     </row>
     <row r="47" spans="1:23" ht="141" customHeight="1">
       <c r="A47" s="5" t="s">
@@ -4054,16 +4095,16 @@
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="3"/>
-      <c r="R47" s="44"/>
-      <c r="S47" s="44" t="s">
+      <c r="R47" s="43"/>
+      <c r="S47" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T47" s="44" t="s">
+      <c r="T47" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="U47" s="45"/>
-      <c r="V47" s="45"/>
-      <c r="W47" s="45"/>
+      <c r="U47" s="44"/>
+      <c r="V47" s="44"/>
+      <c r="W47" s="44"/>
     </row>
     <row r="48" spans="1:23" ht="17">
       <c r="A48" s="34" t="s">
@@ -4079,7 +4120,7 @@
         <v>83</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F48" s="1" t="b">
         <v>0</v>
@@ -4096,21 +4137,21 @@
       </c>
       <c r="O48" s="2"/>
       <c r="P48" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q48" s="3"/>
-      <c r="R48" s="44" t="s">
+      <c r="R48" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S48" s="44" t="s">
+      <c r="S48" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T48" s="44" t="s">
+      <c r="T48" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U48" s="45"/>
-      <c r="V48" s="45"/>
-      <c r="W48" s="45"/>
+      <c r="U48" s="44"/>
+      <c r="V48" s="44"/>
+      <c r="W48" s="44"/>
     </row>
     <row r="49" spans="1:23" ht="17">
       <c r="A49" s="5" t="s">
@@ -4141,14 +4182,14 @@
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="3"/>
-      <c r="R49" s="44" t="s">
+      <c r="R49" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S49" s="44"/>
-      <c r="T49" s="44"/>
-      <c r="U49" s="45"/>
-      <c r="V49" s="45"/>
-      <c r="W49" s="45"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="43"/>
+      <c r="U49" s="44"/>
+      <c r="V49" s="44"/>
+      <c r="W49" s="44"/>
     </row>
     <row r="50" spans="1:23" ht="17">
       <c r="A50" s="5" t="s">
@@ -4179,14 +4220,14 @@
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="3"/>
-      <c r="R50" s="44" t="s">
+      <c r="R50" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S50" s="44"/>
-      <c r="T50" s="44"/>
-      <c r="U50" s="45"/>
-      <c r="V50" s="45"/>
-      <c r="W50" s="45"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="43"/>
+      <c r="U50" s="44"/>
+      <c r="V50" s="44"/>
+      <c r="W50" s="44"/>
     </row>
     <row r="51" spans="1:23" ht="18" thickBot="1">
       <c r="A51" s="34" t="s">
@@ -4202,7 +4243,7 @@
         <v>86</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F51" s="1" t="b">
         <v>0</v>
@@ -4219,21 +4260,21 @@
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q51" s="3"/>
-      <c r="R51" s="44" t="s">
+      <c r="R51" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="S51" s="44" t="s">
+      <c r="S51" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T51" s="44" t="s">
+      <c r="T51" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U51" s="45"/>
-      <c r="V51" s="45"/>
-      <c r="W51" s="45"/>
+      <c r="U51" s="44"/>
+      <c r="V51" s="44"/>
+      <c r="W51" s="44"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W51" xr:uid="{545CA0C1-0282-3A43-9C60-512DE414A571}"/>
@@ -4306,11 +4347,11 @@
       <c r="F1" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="46" t="s">
-        <v>195</v>
+      <c r="H1" s="45" t="s">
+        <v>193</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
@@ -4450,10 +4491,10 @@
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
@@ -4564,7 +4605,7 @@
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>115</v>
@@ -14790,8 +14831,8 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.5" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
     <col min="3" max="3" width="210.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14811,21 +14852,21 @@
         <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="41" t="s">
         <v>154</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14833,10 +14874,10 @@
         <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -14844,32 +14885,32 @@
         <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -14900,13 +14941,13 @@
         <v>37</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -14942,7 +14983,7 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -14956,174 +14997,186 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061FFA46-CE3B-F64A-A906-DBEB47750F41}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E1" s="2"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E2" s="2"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E3" s="2"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E4" s="2"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E5" s="2"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E6" s="2"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E7" s="2"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E8" s="2"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E9" s="2"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E10" s="2"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E11" s="2"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-    </row>
-    <row r="12" spans="1:19" s="39" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q12" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E13" s="2"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E14" s="2"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E15" s="2"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1">
-      <c r="E16" s="2"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" customHeight="1">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>214</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
+        <v>163</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>258</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>